--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488184_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488184_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>2.5739</v>
+        <v>3.2846</v>
       </c>
       <c r="E2" t="n">
-        <v>4.0017</v>
+        <v>4.5893</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.4279</v>
+        <v>-1.3047</v>
       </c>
       <c r="G2" t="n">
         <v>3.1675</v>
@@ -610,13 +610,13 @@
         <v>2.2234</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.5184</v>
+        <v>-0.8077</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.0184</v>
+        <v>-0.4309</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.4999</v>
+        <v>-0.3768</v>
       </c>
       <c r="V2" t="n">
         <v>-0.0016</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.6371</v>
+        <v>2.3358</v>
       </c>
       <c r="E3" t="n">
-        <v>2.4355</v>
+        <v>2.8387</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.7984</v>
+        <v>-0.5029</v>
       </c>
       <c r="G3" t="n">
         <v>0.4308</v>
@@ -688,13 +688,13 @@
         <v>2.9646</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.6472</v>
+        <v>-0.9485</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.8033</v>
+        <v>-0.4001</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.8439</v>
+        <v>-0.5484</v>
       </c>
       <c r="V3" t="n">
         <v>0.63</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.7393999999999999</v>
+        <v>-0.007900000000000001</v>
       </c>
       <c r="E5" t="n">
-        <v>1.7648</v>
+        <v>0.9928</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.0254</v>
+        <v>-1.0008</v>
       </c>
       <c r="G5" t="n">
         <v>-0.9001</v>
@@ -844,13 +844,13 @@
         <v>2.0382</v>
       </c>
       <c r="S5" t="n">
-        <v>1.398</v>
+        <v>0.6506999999999999</v>
       </c>
       <c r="T5" t="n">
-        <v>1.2473</v>
+        <v>0.4754</v>
       </c>
       <c r="U5" t="n">
-        <v>0.1507</v>
+        <v>0.1753</v>
       </c>
       <c r="V5" t="n">
         <v>-0.3144</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>D. JIMENEZ HERRERA</t>
+          <t>R. VARELA SANCHEZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.5706</v>
+        <v>-0.6355</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.9965000000000001</v>
+        <v>0.2453</v>
       </c>
       <c r="F6" t="n">
-        <v>0.4259</v>
+        <v>-0.8808</v>
       </c>
       <c r="G6" t="n">
-        <v>-2.1292</v>
+        <v>0.8541</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.7393</v>
+        <v>1.2918</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.3899</v>
+        <v>-0.4377</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.1838</v>
+        <v>1.0306</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.3912</v>
+        <v>1.0306</v>
       </c>
       <c r="L6" t="n">
-        <v>0.2074</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.9454</v>
+        <v>-0.1766</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.3481</v>
+        <v>0.2611</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.5973</v>
+        <v>-0.4377</v>
       </c>
       <c r="P6" t="n">
-        <v>-2.0382</v>
+        <v>-0.5558999999999999</v>
       </c>
       <c r="Q6" t="n">
-        <v>-4.2616</v>
+        <v>-0.9264</v>
       </c>
       <c r="R6" t="n">
-        <v>2.2234</v>
+        <v>0.3706</v>
       </c>
       <c r="S6" t="n">
-        <v>2.6535</v>
+        <v>0.3252</v>
       </c>
       <c r="T6" t="n">
-        <v>2.1912</v>
+        <v>0.1411</v>
       </c>
       <c r="U6" t="n">
-        <v>0.4623</v>
+        <v>0.184</v>
       </c>
       <c r="V6" t="n">
-        <v>0.9433</v>
+        <v>-1.2589</v>
       </c>
       <c r="W6" t="n">
-        <v>1.2578</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.3144</v>
+        <v>-1.2589</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>R. VARELA SANCHEZ</t>
+          <t>I. LLANO ABASCAL</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.659</v>
+        <v>-0.67</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0495</v>
+        <v>0.6968</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.7085</v>
+        <v>-1.3668</v>
       </c>
       <c r="G7" t="n">
-        <v>0.8541</v>
+        <v>-0.8752</v>
       </c>
       <c r="H7" t="n">
-        <v>1.2918</v>
+        <v>1.1984</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.4377</v>
+        <v>-2.0736</v>
       </c>
       <c r="J7" t="n">
-        <v>1.0306</v>
+        <v>0.7428</v>
       </c>
       <c r="K7" t="n">
-        <v>1.0306</v>
+        <v>1.3956</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>-0.6529</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.1766</v>
+        <v>-1.618</v>
       </c>
       <c r="N7" t="n">
-        <v>0.2611</v>
+        <v>-0.1973</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.4377</v>
+        <v>-1.4207</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.5558999999999999</v>
+        <v>0.9264</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.9264</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0.3706</v>
+        <v>0.9264</v>
       </c>
       <c r="S7" t="n">
-        <v>0.3017</v>
+        <v>-0.7213000000000001</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.0547</v>
+        <v>-0.046</v>
       </c>
       <c r="U7" t="n">
-        <v>0.3564</v>
+        <v>-0.6753</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.2589</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.2589</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>I. LLANO ABASCAL</t>
+          <t>U. CHAGOYEN SALGUERO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,58 +1033,58 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.0864</v>
+        <v>-1.9185</v>
       </c>
       <c r="E8" t="n">
-        <v>0.3051</v>
+        <v>-1.1881</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.3914</v>
+        <v>-0.7302999999999999</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.8752</v>
+        <v>-2.087</v>
       </c>
       <c r="H8" t="n">
-        <v>1.1984</v>
+        <v>-0.213</v>
       </c>
       <c r="I8" t="n">
-        <v>-2.0736</v>
+        <v>-1.874</v>
       </c>
       <c r="J8" t="n">
-        <v>0.7428</v>
+        <v>-1.2198</v>
       </c>
       <c r="K8" t="n">
-        <v>1.3956</v>
+        <v>0.0859</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.6529</v>
+        <v>-1.3057</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.618</v>
+        <v>-0.8671</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.1973</v>
+        <v>-0.2989</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.4207</v>
+        <v>-0.5683</v>
       </c>
       <c r="P8" t="n">
-        <v>0.9264</v>
+        <v>0.1853</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0.9264</v>
+        <v>0.1853</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.1376</v>
+        <v>-0.0168</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.4377</v>
+        <v>0.0317</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.6999</v>
+        <v>-0.0485</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>U. CHAGOYEN SALGUERO</t>
+          <t>D. JIMENEZ HERRERA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.2183</v>
+        <v>-2.7956</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.4387</v>
+        <v>-2.7045</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.7796</v>
+        <v>-0.0911</v>
       </c>
       <c r="G9" t="n">
-        <v>-2.087</v>
+        <v>-2.1292</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.213</v>
+        <v>-0.7393</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.874</v>
+        <v>-1.3899</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.2198</v>
+        <v>-0.1838</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0859</v>
+        <v>-0.3912</v>
       </c>
       <c r="L9" t="n">
-        <v>-1.3057</v>
+        <v>0.2074</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.8671</v>
+        <v>-1.9454</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.2989</v>
+        <v>-0.3481</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.5683</v>
+        <v>-1.5973</v>
       </c>
       <c r="P9" t="n">
-        <v>0.1853</v>
+        <v>-2.0382</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-4.2616</v>
       </c>
       <c r="R9" t="n">
-        <v>0.1853</v>
+        <v>2.2234</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.3166</v>
+        <v>0.4284</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.2189</v>
+        <v>0.4831</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.0977</v>
+        <v>-0.0547</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>0.9433</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.2578</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-0.3144</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.8733</v>
+        <v>-3.3481</v>
       </c>
       <c r="E10" t="n">
-        <v>-4.6989</v>
+        <v>-4.0999</v>
       </c>
       <c r="F10" t="n">
-        <v>0.8257</v>
+        <v>0.7518</v>
       </c>
       <c r="G10" t="n">
         <v>-3.2829</v>
@@ -1234,13 +1234,13 @@
         <v>2.4087</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.7020999999999999</v>
+        <v>-0.1769</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.0732</v>
+        <v>-0.4741</v>
       </c>
       <c r="U10" t="n">
-        <v>0.371</v>
+        <v>0.2972</v>
       </c>
       <c r="V10" t="n">
         <v>-0.6294</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>R. ORTEGA MORA</t>
+          <t>F. RUESGA MORALES</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-5.0102</v>
+        <v>-4.493</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.5984</v>
+        <v>-4.4773</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.4118</v>
+        <v>-0.0157</v>
       </c>
       <c r="G11" t="n">
-        <v>-2.5092</v>
+        <v>-1.0765</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.6568</v>
+        <v>-0.8461</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.8524</v>
+        <v>-0.2304</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.1984</v>
+        <v>0.0795</v>
       </c>
       <c r="K11" t="n">
-        <v>-1.1984</v>
+        <v>-1.3104</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>1.3899</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.3108</v>
+        <v>-1.156</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.4584</v>
+        <v>0.4643</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.8524</v>
+        <v>-1.6203</v>
       </c>
       <c r="P11" t="n">
-        <v>-2.2234</v>
+        <v>-2.594</v>
       </c>
       <c r="Q11" t="n">
-        <v>-2.7793</v>
+        <v>-5.3733</v>
       </c>
       <c r="R11" t="n">
-        <v>0.5558999999999999</v>
+        <v>2.7793</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.2776</v>
+        <v>-0.1937</v>
       </c>
       <c r="T11" t="n">
-        <v>0.3793</v>
+        <v>-0.4424</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.6568000000000001</v>
+        <v>0.2487</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>-0.6289</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.2589</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>-1.8877</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>F. RUESGA MORALES</t>
+          <t>R. ORTEGA MORA</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-5.5588</v>
+        <v>-5.2307</v>
       </c>
       <c r="E12" t="n">
-        <v>-5.2723</v>
+        <v>-3.7942</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.2865</v>
+        <v>-1.4364</v>
       </c>
       <c r="G12" t="n">
-        <v>-1.0765</v>
+        <v>-2.5092</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.8461</v>
+        <v>-1.6568</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.2304</v>
+        <v>-0.8524</v>
       </c>
       <c r="J12" t="n">
-        <v>0.0795</v>
+        <v>-1.1984</v>
       </c>
       <c r="K12" t="n">
-        <v>-1.3104</v>
+        <v>-1.1984</v>
       </c>
       <c r="L12" t="n">
-        <v>1.3899</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>-1.156</v>
+        <v>-1.3108</v>
       </c>
       <c r="N12" t="n">
-        <v>0.4643</v>
+        <v>-0.4584</v>
       </c>
       <c r="O12" t="n">
-        <v>-1.6203</v>
+        <v>-0.8524</v>
       </c>
       <c r="P12" t="n">
-        <v>-2.594</v>
+        <v>-2.2234</v>
       </c>
       <c r="Q12" t="n">
-        <v>-5.3733</v>
+        <v>-2.7793</v>
       </c>
       <c r="R12" t="n">
-        <v>2.7793</v>
+        <v>0.5558999999999999</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.2595</v>
+        <v>-0.498</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.2373</v>
+        <v>0.1834</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.0222</v>
+        <v>-0.6815</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.6289</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>1.2589</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.8877</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -1423,16 +1423,16 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-12.46</v>
+        <v>-11.9127</v>
       </c>
       <c r="E13" t="n">
-        <v>-5.882000000000001</v>
+        <v>-5.334900000000001</v>
       </c>
       <c r="F13" t="n">
-        <v>-6.5779</v>
+        <v>-6.577699999999999</v>
       </c>
       <c r="G13" t="n">
-        <v>-6.841500000000001</v>
+        <v>-6.8415</v>
       </c>
       <c r="H13" t="n">
         <v>8.211399999999999</v>
@@ -1441,7 +1441,7 @@
         <v>-15.0529</v>
       </c>
       <c r="J13" t="n">
-        <v>5.4926</v>
+        <v>5.492599999999999</v>
       </c>
       <c r="K13" t="n">
         <v>8.181800000000001</v>
@@ -1453,7 +1453,7 @@
         <v>-12.334</v>
       </c>
       <c r="N13" t="n">
-        <v>0.02940000000000009</v>
+        <v>0.02939999999999998</v>
       </c>
       <c r="O13" t="n">
         <v>-12.3635</v>
@@ -1468,10 +1468,10 @@
         <v>16.6758</v>
       </c>
       <c r="S13" t="n">
-        <v>-2.5058</v>
+        <v>-1.9586</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.0257</v>
+        <v>-0.4788000000000001</v>
       </c>
       <c r="U13" t="n">
         <v>-1.48</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>9.8649</v>
+        <v>7.5691</v>
       </c>
       <c r="E14" t="n">
-        <v>9.9436</v>
+        <v>7.985</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.07870000000000001</v>
+        <v>-0.4159</v>
       </c>
       <c r="G14" t="n">
         <v>5.4155</v>
@@ -1546,13 +1546,13 @@
         <v>2.0382</v>
       </c>
       <c r="S14" t="n">
-        <v>4.135</v>
+        <v>1.8392</v>
       </c>
       <c r="T14" t="n">
-        <v>3.1176</v>
+        <v>1.159</v>
       </c>
       <c r="U14" t="n">
-        <v>1.0174</v>
+        <v>0.6802</v>
       </c>
       <c r="V14" t="n">
         <v>0.3144</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.788</v>
+        <v>5.0423</v>
       </c>
       <c r="E15" t="n">
-        <v>4.5097</v>
+        <v>4.4118</v>
       </c>
       <c r="F15" t="n">
-        <v>0.2783</v>
+        <v>0.6304999999999999</v>
       </c>
       <c r="G15" t="n">
         <v>5.0251</v>
@@ -1624,13 +1624,13 @@
         <v>2.4087</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.3111</v>
+        <v>-0.0569</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.2014</v>
+        <v>-0.2994</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.1097</v>
+        <v>0.2425</v>
       </c>
       <c r="V15" t="n">
         <v>0.63</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>4.0223</v>
+        <v>4.9111</v>
       </c>
       <c r="E16" t="n">
-        <v>2.7596</v>
+        <v>3.6409</v>
       </c>
       <c r="F16" t="n">
-        <v>1.2627</v>
+        <v>1.2702</v>
       </c>
       <c r="G16" t="n">
         <v>1.8428</v>
@@ -1702,13 +1702,13 @@
         <v>3.3352</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.6554</v>
+        <v>0.2335</v>
       </c>
       <c r="T16" t="n">
-        <v>-1.0184</v>
+        <v>-0.1371</v>
       </c>
       <c r="U16" t="n">
-        <v>0.3631</v>
+        <v>0.3705</v>
       </c>
       <c r="V16" t="n">
         <v>-0.315</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.781</v>
+        <v>3.2963</v>
       </c>
       <c r="E17" t="n">
-        <v>1.4346</v>
+        <v>1.7284</v>
       </c>
       <c r="F17" t="n">
-        <v>1.3463</v>
+        <v>1.5679</v>
       </c>
       <c r="G17" t="n">
         <v>1.5509</v>
@@ -1780,13 +1780,13 @@
         <v>1.297</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.2141</v>
+        <v>0.3013</v>
       </c>
       <c r="T17" t="n">
-        <v>0.1604</v>
+        <v>0.4542</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.3746</v>
+        <v>-0.153</v>
       </c>
       <c r="V17" t="n">
         <v>1.2589</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>M. MOLINA LOPEZ</t>
+          <t>D. MOUHAMED KHALIFA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.0615</v>
+        <v>-0.2054</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.5664</v>
+        <v>-1.4502</v>
       </c>
       <c r="F19" t="n">
-        <v>1.6279</v>
+        <v>1.2448</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.8022</v>
+        <v>-0.2888</v>
       </c>
       <c r="H19" t="n">
-        <v>-2.0572</v>
+        <v>-1.1322</v>
       </c>
       <c r="I19" t="n">
-        <v>0.255</v>
+        <v>0.8434</v>
       </c>
       <c r="J19" t="n">
-        <v>-2.3797</v>
+        <v>-0.7591</v>
       </c>
       <c r="K19" t="n">
-        <v>-1.8512</v>
+        <v>-0.8421</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.5284</v>
+        <v>0.0829</v>
       </c>
       <c r="M19" t="n">
-        <v>0.5774</v>
+        <v>0.4703</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.206</v>
+        <v>-0.2901</v>
       </c>
       <c r="O19" t="n">
-        <v>0.7834</v>
+        <v>0.7604</v>
       </c>
       <c r="P19" t="n">
-        <v>1.1117</v>
+        <v>0.3706</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-0.9264</v>
       </c>
       <c r="R19" t="n">
-        <v>1.1117</v>
+        <v>1.297</v>
       </c>
       <c r="S19" t="n">
-        <v>1.0665</v>
+        <v>0.3423</v>
       </c>
       <c r="T19" t="n">
-        <v>0.8133</v>
+        <v>0.2354</v>
       </c>
       <c r="U19" t="n">
-        <v>0.2532</v>
+        <v>0.1069</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.3144</v>
+        <v>-0.6294</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.3144</v>
+        <v>-0.6294</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>J. PINILLA NUNEZ</t>
+          <t>M. MOLINA LOPEZ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,64 +1969,64 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.434</v>
+        <v>-0.3794</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.4503</v>
+        <v>-1.9581</v>
       </c>
       <c r="F20" t="n">
-        <v>1.0163</v>
+        <v>1.5787</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.014</v>
+        <v>-1.8022</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.673</v>
+        <v>-2.0572</v>
       </c>
       <c r="I20" t="n">
-        <v>0.659</v>
+        <v>0.255</v>
       </c>
       <c r="J20" t="n">
-        <v>0.1254</v>
+        <v>-2.3797</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.7562</v>
+        <v>-1.8512</v>
       </c>
       <c r="L20" t="n">
-        <v>0.8816000000000001</v>
+        <v>-0.5284</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.1394</v>
+        <v>0.5774</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.9167999999999999</v>
+        <v>-0.206</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.2226</v>
+        <v>0.7834</v>
       </c>
       <c r="P20" t="n">
-        <v>0.1853</v>
+        <v>1.1117</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.8529</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>2.0382</v>
+        <v>1.1117</v>
       </c>
       <c r="S20" t="n">
-        <v>0.3947</v>
+        <v>0.6254999999999999</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.0373</v>
+        <v>0.4216</v>
       </c>
       <c r="U20" t="n">
-        <v>0.432</v>
+        <v>0.2039</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>-0.3144</v>
       </c>
       <c r="W20" t="n">
-        <v>0.3144</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
         <v>-0.3144</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>D. MOUHAMED KHALIFA</t>
+          <t>J. PINILLA NUNEZ</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.5484</v>
+        <v>-0.5004</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.744</v>
+        <v>-1.4503</v>
       </c>
       <c r="F21" t="n">
-        <v>1.1956</v>
+        <v>0.9499</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.2888</v>
+        <v>-1.014</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.1322</v>
+        <v>-1.673</v>
       </c>
       <c r="I21" t="n">
-        <v>0.8434</v>
+        <v>0.659</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.7591</v>
+        <v>0.1254</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.8421</v>
+        <v>-0.7562</v>
       </c>
       <c r="L21" t="n">
-        <v>0.0829</v>
+        <v>0.8816000000000001</v>
       </c>
       <c r="M21" t="n">
-        <v>0.4703</v>
+        <v>-1.1394</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.2901</v>
+        <v>-0.9167999999999999</v>
       </c>
       <c r="O21" t="n">
-        <v>0.7604</v>
+        <v>-0.2226</v>
       </c>
       <c r="P21" t="n">
-        <v>0.3706</v>
+        <v>0.1853</v>
       </c>
       <c r="Q21" t="n">
-        <v>-0.9264</v>
+        <v>-1.8529</v>
       </c>
       <c r="R21" t="n">
-        <v>1.297</v>
+        <v>2.0382</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.0007</v>
+        <v>0.3283</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.0584</v>
+        <v>-0.0373</v>
       </c>
       <c r="U21" t="n">
-        <v>0.0577</v>
+        <v>0.3656</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.6294</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>0.3144</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.6294</v>
+        <v>-0.3144</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.0801</v>
+        <v>-0.7622</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.8388</v>
+        <v>-0.4471</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.2413</v>
+        <v>-0.3151</v>
       </c>
       <c r="G22" t="n">
         <v>0.1764</v>
@@ -2170,13 +2170,13 @@
         <v>1.6676</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.4074</v>
+        <v>-0.0895</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.4377</v>
+        <v>-0.046</v>
       </c>
       <c r="U22" t="n">
-        <v>0.0303</v>
+        <v>-0.0435</v>
       </c>
       <c r="V22" t="n">
         <v>-2.5166</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-5.3392</v>
+        <v>-4.2025</v>
       </c>
       <c r="E25" t="n">
-        <v>-6.1023</v>
+        <v>-5.5147</v>
       </c>
       <c r="F25" t="n">
-        <v>0.7631</v>
+        <v>1.3123</v>
       </c>
       <c r="G25" t="n">
         <v>-2.7363</v>
@@ -2404,13 +2404,13 @@
         <v>3.3352</v>
       </c>
       <c r="S25" t="n">
-        <v>-1.1734</v>
+        <v>-0.0367</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.5296999999999999</v>
+        <v>0.0579</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.6437</v>
+        <v>-0.0945</v>
       </c>
       <c r="V25" t="n">
         <v>2.8321</v>
@@ -2437,16 +2437,16 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>12.46</v>
+        <v>13.1129</v>
       </c>
       <c r="E26" t="n">
-        <v>6.5779</v>
+        <v>6.577900000000001</v>
       </c>
       <c r="F26" t="n">
-        <v>5.882000000000001</v>
+        <v>6.5351</v>
       </c>
       <c r="G26" t="n">
-        <v>6.841599999999998</v>
+        <v>6.841599999999996</v>
       </c>
       <c r="H26" t="n">
         <v>-8.211399999999999</v>
@@ -2473,7 +2473,7 @@
         <v>2.6893</v>
       </c>
       <c r="P26" t="n">
-        <v>1.8529</v>
+        <v>1.852900000000001</v>
       </c>
       <c r="Q26" t="n">
         <v>-16.6759</v>
@@ -2482,13 +2482,13 @@
         <v>18.5288</v>
       </c>
       <c r="S26" t="n">
-        <v>2.5059</v>
+        <v>3.1588</v>
       </c>
       <c r="T26" t="n">
-        <v>1.4802</v>
+        <v>1.4801</v>
       </c>
       <c r="U26" t="n">
-        <v>1.0257</v>
+        <v>1.6786</v>
       </c>
       <c r="V26" t="n">
         <v>1.26</v>
